--- a/data_extactor/batch_10_fa/batch_0021_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0021_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخنوری | نوشتن | گوش دادن فعال | ریاضیات | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | مکانیک | رایانه‌ها و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | حمل و نقل | طراحی | خدمات مشتری و شخصی | آموزش و پرورش</t>
+          <t>مهندسی و فناوری | مکانیک | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | حمل و نقل | طراحی | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک نوشتاری | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | استدلال استقرایی | درک شنیداری | نظم‌دهی اطلاعات | بیان شفاهی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | بیان نوشتاری | وضوح گفتار | تشخیص گفتار | توجه انتخابی | ثبات دست و بازو | مهارت دستی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | دید دور | دقت کنترل | استدلال ریاضی | خلاقیت | روانی ایده‌ها</t>
+          <t>درک کتبی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | درک شفاهی | ترتیب‌دهی اطلاعات | بیان شفاهی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | بیان کتبی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | ثبات دست و بازو | مهارت دستی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور | دقت کنترل | استدلال ریاضی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | سلامت و ایمنی سایر کارکنان | فشار زمانی | در وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | نزدیکی فیزیکی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | فشار زمانی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | مهندسان هوافضا | مهندسان خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های اویونیک | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران برق و الکترونیک، تجهیزات حمل و نقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز رایانه | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | مهندسان خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخنوری | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | مهندسی و فناوری | رایانه‌ها و الکترونیک | فیزیک | مکانیک | زبان انگلیسی | تولید و پردازش | طراحی</t>
+          <t>ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | فیزیک | مکانیک | زبان انگلیسی | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند اندام | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | پیامد خطا | محیط داخلی، بدون کنترل محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار کارهای مشابه | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | پیامد خطا | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | تکنسین‌های شیمی | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات برق و الکترونیک | نصاب‌ها و تعمیرکاران برق و الکترونیک، تجهیزات حمل و نقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز رایانه | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | بازرسان، آزمایش‌کنندگان، مرتب‌کنندگان، نمونه‌گیران و وزن‌کنندگان | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های هوانوردی | تکنسین‌های شیمی | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | نرم‌افزار شبیه‌سازی ANSYS | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | نرم‌افزار طراحی به کمک رایانه سه‌بعدی 3D CAD | نرم‌افزار طراحی به کمک رایانه دوبعدی 2D CAD | نرم‌افزار ایمیل | Microsoft PowerPoint | نرم‌افزار کنترل فرآیند آماری SPC | Minitab</t>
+          <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | نرم‌افزار شبیه‌سازی ANSYS | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | نرم‌افزار طراحی سه بعدی به کمک کامپیوتر CAD | نرم‌افزار طراحی دو بعدی به کمک کامپیوتر CAD | نرم‌افزار ایمیل | Microsoft PowerPoint | نرم‌افزار کنترل فرآیند آماری SPC | Minitab</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخنوری | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | رایانه‌ها و الکترونیک | فیزیک | مکانیک | زبان انگلیسی | طراحی | تولید و پردازش</t>
+          <t>مهندسی و فناوری | ریاضیات | رایانه و الکترونیک | فیزیک | مکانیک | زبان انگلیسی | طراحی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند اندام | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل محیطی | اهمیت دقیق یا صحیح بودن | پیامد خطا | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | اهمیت تکرار کارهای مشابه</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | پیامد خطا | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان تست غیرمخرب | تکنسین‌های فوتونیک | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های رباتیک | تکنولوژیست‌ها و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های مهندسی خودرو | تکنسین‌های نقشه‌برداری و نقشه‌کشی | نقشه‌کش‌های معماری و عمرانی | نقشه‌کش‌های مکانیک | نقشه‌کش‌های برق و الکترونیک | مهندسان صنایع | مهندسان مکانیک | مدیران سیستم‌های کنترل کیفیت</t>
+          <t>متخصصان تست غیرمخرب | تکنسین‌های فوتونیک | تکنسین‌ها و کارشناسان مهندسی عمران | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های رباتیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های مهندسی خودرو | تکنسین‌های نقشه‌برداری و نقشه‌کشی | نقشه‌کشان معماری و عمران | نقشه‌کشان مکانیک | نقشه‌کشان برق و الکترونیک | مهندسان صنایع | مهندسان مکانیک | مدیران سیستم‌های کنترل کیفیت</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نوشتن | استراتژی‌های یادگیری | سخنوری | ریاضیات | علوم</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری | سخن گفتن | ریاضیات | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | رایانه‌ها و الکترونیک | تولید و پردازش | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | ایمنی و امنیت عمومی | طراحی | ساختمان و ساخت و ساز</t>
+          <t>مهندسی و فناوری | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | رایانه و الکترونیک | تولید و فرآوری | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | ایمنی و امنیت عمومی | طراحی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک نوشتاری | استدلال قیاسی | درک شنیداری | استدلال استقرایی | نظم‌دهی اطلاعات | بیان شفاهی | دید دور | بیان نوشتاری | وضوح گفتار | انعطاف‌پذیری بستار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | دقت کنترل | توجه انتخابی | تجسم | سرعت ادراکی | ثبات دست و بازو | تشخیص رنگ بصری | مهارت دستی | سرعت بستار | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک کتبی | استدلال قیاسی | درک شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی | بینایی دور | بیان کتبی | وضوح گفتار | انعطاف‌پذیری بستار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | دقت کنترل | توجه انتخابی | تجسم | سرعت ادراکی | ثبات دست و بازو | تشخیص رنگ بصری | مهارت دستی | سرعت بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تکرار تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم | محیط داخلی، بدون کنترل محیطی | محیط داخلی، دارای کنترل محیطی | محیط خارجی، قرار گرفتن در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط خارجی، زیر پوشش | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | اهمیت تکرار کارهای مشابه | نامه‌ها و یادداشت‌های کتبی | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر اشعه | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | مکالمات تلفنی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، بدون کنترل شرایط محیطی | محیط داخلی، دارای کنترل شرایط محیطی | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، زیر سقف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | تکنسین‌های مهندسی خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | بازرسان، آزمایش‌کنندگان، مرتب‌کنندگان، نمونه‌گیران و وزن‌کنندگان | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | تکنولوژیست‌ها و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های نظارت هسته‌ای | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های نظارت هسته‌ای | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نوشتن | سخنوری</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه‌ها و الکترونیک | ریاضیات | مکانیک | زبان انگلیسی | تولید و پردازش | فیزیک | خدمات مشتری و شخصی</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | مکانیک | زبان انگلیسی | تولید و فرآوری | فیزیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شنیداری | حساسیت به مسئله | درک نوشتاری | نظم‌دهی اطلاعات | مهارت انگشتان | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | دقت کنترل | مهارت دستی | ثبات دست و بازو | تجسم | تشخیص گفتار | تشخیص رنگ بصری | توجه انتخابی | وضوح گفتار</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | مهارت انگشتان | بیان شفاهی | بیان کتبی | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | دقت کنترل | مهارت دستی | ثبات دست و بازو | تجسم | تشخیص گفتار | تشخیص رنگ بصری | توجه انتخابی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های حضوری با افراد و درون تیم‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | تکنسین‌های مهندسی خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران برق و الکترونیک، تجهیزات حمل و نقل | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز رایانه | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | مهندسان میکروسیستم | تکنولوژیست‌ها و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های آزمایشگاه چشم‌پزشکی | مهندسان فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | مهندسان میکروسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های آزمایشگاه چشم‌پزشکی | مهندسان فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3D Nature LLC Visual Nature Studio | 3D Nature LLC World Construction Set | Adobe Acrobat Writer | Adobe FreeHand MX | Adobe Illustrator | Adobe Photoshop | Autodesk 3d Studio Viz | Autodesk AutoCAD | Autodesk AutoCAD Blue Sky | Autodesk AutoCAD Civil 3D | Autodesk AutoCAD Map 3D | Autodesk CAiCE Visual Transportation | Autodesk Land Desktop | Bentley GEOPAK Civil Engineering Suite | Bentley GeoPak Bridge | Bentley MicroStation | Bentley Systems InRoads Suite | CARIS HIPS | CARIS SIPS | Carlson SurvCADD | Carlson Survey | نرم‌افزار طراحی و نقشه‌کشی به کمک رایانه CADD | نرم‌افزار هندسه مختصات COGO | نرم‌افزار پایگاه داده | نرم‌افزار Datalog with guidance DLWG | سیستم فتوگرامتری دیجیتال رومیزی DDPS | نرم‌افزار مدل ارتفاع دیجیتال DEM | ESRI ArcCatalog | ESRI ArcEditor | ESRI ArcGIS (ویژگی تحلیلی یا علمی) | ESRI ArcGIS ArcPy | ESRI ArcGIS Spatial Analyst | نرم‌افزار ESRI ArcGIS | ESRI ArcIMS | ESRI ArcInfo | ESRI ArcSDE | ESRI ArcToolbox | ESRI ArcView | ESRI ArcView 3D Analyst | ESRI MapObjects | ESRI Maplex | ESRI Personal Geodatabase | نرم‌افزار ایمیل | Foresoft CDS Cogo | Foresoft CDS Model | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | نرم‌افزار گرافیک | Hexagon Geospatial Imagine Photogrammetry | Hexagon Intergraph | زبان نشانه‌گذاری ابرمتن HTML | IMAGINE OrthoBASE | JavaScript | Leica Geosystems ERDAS IMAGINE | نرم‌افزار درایور سطح پایین LLD | MENSI 3Dipsos | MapInfo | نرم‌افزار نقشه‌کشی | MicroSurvey FieldGenius | MicroSurvey OfficeSync | MicroSurvey Star*Net | MicroSurveyCAD | Microsoft Access | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | نسخه اسکریپت‌نویسی Microsoft Visual Basic VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Word | نرم‌افزار مدل‌سازی | Muncy Plat Pronto | PCI Geomatics eCognition | نرم‌افزار PCI Geomatics | Python | QuarkXPress | QuickCogo | RockWare ArcMap | SiteComp Survey | کتابخانه‌های نرم‌افزاری | زبان پرس‌وجوی ساختاریافته SQL | TELEDYNE CARIS | TRS Software TomCADD | Traverse PC | Trimble Digital Fieldbook | Trimble GPS Pathfinder Office | Trimble Geomatics Office | Trimble TerraSync | Trimble Terramodel | Trimble Total Control | Tripod Data Systems COGO | Tripod Data Systems Foresight | نرم‌افزار Tripod Data Systems | Triton Elics International Isis | نرم‌افزار مرورگر وب</t>
+          <t>3D Nature LLC Visual Nature Studio | 3D Nature LLC World Construction Set | Adobe Acrobat Writer | Adobe FreeHand MX | Adobe Illustrator | Adobe Photoshop | Autodesk 3d Studio Viz | Autodesk AutoCAD | Autodesk AutoCAD Blue Sky | Autodesk AutoCAD Civil 3D | Autodesk AutoCAD Map 3D | Autodesk CAiCE Visual Transportation | Autodesk Land Desktop | Bentley GEOPAK Civil Engineering Suite | Bentley GeoPak Bridge | Bentley MicroStation | Bentley Systems InRoads Suite | CARIS HIPS | CARIS SIPS | Carlson SurvCADD | Carlson Survey | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار هندسه مختصات COGO | نرم‌افزار پایگاه داده | نرم‌افزار Datalog with guidance DLWG | سیستم فتوگرامتری دیجیتال رومیزی DDPS | نرم‌افزار مدل ارتفاع دیجیتال DEM | ESRI ArcCatalog | ESRI ArcEditor | ESRI ArcGIS (ویژگی تحلیلی یا علمی) | ESRI ArcGIS ArcPy | ESRI ArcGIS Spatial Analyst | نرم‌افزار ESRI ArcGIS | ESRI ArcIMS | ESRI ArcInfo | ESRI ArcSDE | ESRI ArcToolbox | ESRI ArcView | ESRI ArcView 3D Analyst | ESRI MapObjects | ESRI Maplex | ESRI Personal Geodatabase | نرم‌افزار ایمیل | Foresoft CDS Cogo | Foresoft CDS Model | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | نرم‌افزار گرافیکی | Hexagon Geospatial Imagine Photogrammetry | Hexagon Intergraph | زبان نشانه‌گذاری ابرمتن HTML | IMAGINE OrthoBASE | JavaScript | Leica Geosystems ERDAS IMAGINE | نرم‌افزار درایور سطح پایین LLD | MENSI 3Dipsos | MapInfo | نرم‌افزار نقشه‌برداری | MicroSurvey FieldGenius | MicroSurvey OfficeSync | MicroSurvey Star*Net | MicroSurveyCAD | Microsoft Access | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Word | نرم‌افزار مدل‌سازی | Muncy Plat Pronto | PCI Geomatics eCognition | نرم‌افزار PCI Geomatics | Python | QuarkXPress | QuickCogo | RockWare ArcMap | SiteComp Survey | کتابخانه‌های نرم‌افزاری | زبان پرس‌وجوی ساختاریافته SQL | TELEDYNE CARIS | TRS Software TomCADD | Traverse PC | Trimble Digital Fieldbook | Trimble GPS Pathfinder Office | Trimble Geomatics Office | Trimble TerraSync | Trimble Terramodel | Trimble Total Control | Tripod Data Systems COGO | Tripod Data Systems Foresight | نرم‌افزار Tripod Data Systems | Triton Elics International Isis | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نوشتن | ریاضیات | نظارت | گوش دادن فعال | سخنوری | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | ریاضیات | نظارت | گوش دادن فعال | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه‌ها و الکترونیک | جغرافیا | ریاضیات | زبان انگلیسی | مهندسی و فناوری | طراحی | خدمات مشتری و شخصی</t>
+          <t>رایانه و الکترونیک | جغرافیا | ریاضیات | زبان انگلیسی | مهندسی و فناوری | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک نوشتاری | دید نزدیک | استدلال استقرایی | بیان شفاهی | درک شنیداری | حساسیت به مسئله | استدلال قیاسی | نظم‌دهی اطلاعات | بیان نوشتاری | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | دید دور | روانی ایده‌ها</t>
+          <t>درک کتبی | بینایی نزدیک | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | بینایی دور | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق یا صحیح بودن | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | اهمیت تکرار کارهای مشابه | کار با یا مشارکت در یک گروه کاری یا تیم | تکرار تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | صرف زمان برای انجام حرکات تکراری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | صرف زمان برای انجام حرکات تکراری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نقشه‌کش‌های معماری و عمرانی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | کارتوگراف‌ها و فتوگرامتریست‌ها | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | دانشمندان داده | نقشه‌کش‌های برق و الکترونیک | نقشه‌برداران ژئودتیک | جغرافیدانان | تکنولوژیست‌ها و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | زمین‌شناسان، به جز هیدرولوژیست‌ها و جغرافیدانان | تکنسین‌های هیدرولوژی | هیدرولوژیست‌ها | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | دانشمندان و تکنولوژیست‌های سنجش از دور | تکنسین‌های سنجش از دور | دستیاران آماری | نقشه‌برداران | تکنسین‌های ترافیک</t>
+          <t>نقشه‌کشان معماری و عمران | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نقشه‌برداران و فتوگرامتریست‌ها | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | دانشمندان داده | نقشه‌کشان برق و الکترونیک | نقشه‌برداران ژئودتیک | جغرافیدانان | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | آب‌شناسان | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | دستیاران آماری | نقشه‌برداران | تکنسین‌های ترافیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم | نوشتن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال | سخنوری | نظارت | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | علوم | نگارش | تفکر انتقادی | یادگیری فعال | گوش دادن فعال | سخن گفتن | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | ریاضیات | زبان انگلیسی | شیمی | تولید مواد غذایی | آموزش و پرورش | خدمات مشتری و شخصی | رایانه‌ها و الکترونیک | فروش و بازاریابی | مدیریت و اداره</t>
+          <t>زیست‌شناسی | ریاضیات | زبان انگلیسی | شیمی | تولید مواد غذایی | آموزش و پرورش | خدمات مشتری و شخصی | رایانه و الکترونیک | فروش و بازاریابی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شنیداری | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید نزدیک | تشخیص گفتار | روانی ایده‌ها | خلاقیت | استدلال ریاضی | تسهیل اعداد | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | دید دور</t>
+          <t>وضوح گفتار | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | اصالت | استدلال ریاضی | توانایی عددی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | در وسیله نقلیه محصور یا کار با تجهیزات محصور | تکرار تصمیم‌گیری | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | برخورد با مشتریان خارجی یا عموم مردم</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | معلمان علوم کشاورزی، پس از متوسطه | تکنسین‌های کشاورزی | پرورش‌دهندگان حیوانات | بیوشیمی‌دانان و بیوفیزیک‌دانان | تکنسین‌های بیولوژیکی | زیست‌شناسان | تکنسین‌های رژیم غذایی | متخصصان رژیم غذایی و تغذیه | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران مزرعه، حیوانات مزرعه، دامداری و آبزی‌پروری | تکنسین‌های علوم غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | ژنتیک‌دانان | میکروبیولوژیست‌ها | دانشمندان خاک و گیاه | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>بازرسان کشاورزی | مدرسان علوم کشاورزی، پس از متوسطه | تکنسین‌های کشاورزی | پرورش‌دهندگان حیوانات | بیوشیمی‌دانان و بیوفیزیک‌دانان | تکنسین‌های زیستی | زیست‌شناسان | تکنسین‌های رژیم غذایی | متخصصان رژیم غذایی و تغذیه | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | تکنسین‌های علوم غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | ژنتیک‌دان‌ها | میکروبیولوژیست‌ها | دانشمندان خاک و گیاه | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BioDiscovery ImaGene | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | نرم‌افزار تحلیل تصویر | Insightful S-PLUS | MDS Analytical Technologies GenePix Pro | اتوماسیون بازاریابی Marketo | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Eloqua | PathogenTracker | R | نرم‌افزار SAP | STATISTICA | سیستم‌های کامپیوتری حسی SIMS | زبان پرس‌وجوی ساختاریافته SQL | Tableau | پایگاه داده ملی مواد مغذی USDA وزارت کشاورزی ایالات متحده</t>
+          <t>BioDiscovery ImaGene | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | نرم‌افزار تحلیل تصویر | Insightful S-PLUS | MDS Analytical Technologies GenePix Pro | Marketo Marketing Automation | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Eloqua | PathogenTracker | R | نرم‌افزار SAP | STATISTICA | سیستم‌های کامپیوتری حسی SIMS | زبان پرس‌وجوی ساختاریافته SQL | Tableau | پایگاه داده ملی مواد مغذی USDA وزارت کشاورزی ایالات متحده</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | درک مطلب | گوش دادن فعال | نوشتن | سخنوری | علوم | نظارت | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>یادگیری فعال | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | علوم | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و پردازش | تولید مواد غذایی | شیمی | زبان انگلیسی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | رایانه‌ها و الکترونیک | مدیریت و اداره | آموزش و پرورش | خدمات مشتری و شخصی | قانون و دولت | اداری</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | شیمی | زبان انگلیسی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | رایانه و الکترونیک | مدیریت و اداره | آموزش و پرورش | خدمات مشتری و شخصی | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | تسهیل اعداد | استدلال ریاضی | سرعت ادراکی | تشخیص رنگ بصری | دید دور | سرعت بستار | توجه انتخابی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | سرعت ادراکی | تشخیص رنگ بصری | بینایی دور | سرعت بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | بازرسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان علوم دامی | تکنسین‌های پردازش سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | آشپزها، رستوران | تکنسین‌های علوم غذایی | درجه‌بندی‌کنندگان و مرتب‌کنندگان، محصولات کشاورزی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | اکولوژیست‌های صنعتی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | میکروبیولوژیست‌ها | تحلیل‌گران کنترل کیفیت | دانشمندان خاک و گیاه</t>
+          <t>مهندسان کشاورزی | بازرسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | آشپزها، رستوران | تکنسین‌های علوم غذایی | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | میکروبیولوژیست‌ها | تحلیل‌گران کنترل کیفیت | دانشمندان خاک و گیاه</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3dMapper | Autodesk AutoCAD | نرم‌افزار ESRI ArcGIS | ماشین‌حساب تأثیر بهره‌وری فرسایش EPIC | مدل فرسایش خاک اروپا EUROSEM | GAEA Technologies WinSieve | GEOEAS | GSLIB | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Gstat | IBM SPSS Statistics | LandSerf | Leica Geosystems ERDAS IMAGINE | Microsoft Access | صفحات سرور فعال Microsoft ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | برنامه توصیف PEDON خدمات حفاظت از منابع ملی NRCS | کاوشگر خاک خدمات حفاظت از منابع ملی NRCS | سیستم اطلاعات خاک ملی NASIS | PC-Progress HYDRUS | PedonCE | R | SAS | SGeMS | SPAW | STATISTICA | پایگاه‌های داده اطلاعات خاک | SoilVision Systems SVOFFICE | UNSATFLOW | تخمین واریوگرام و پیش‌بینی فضایی به علاوه خطا Vesper | پروژه پیش‌بینی فرسایش آب WEPP</t>
+          <t>3dMapper | Autodesk AutoCAD | نرم‌افزار ESRI ArcGIS | ماشین‌حساب تأثیر بهره‌وری فرسایش EPIC | مدل فرسایش خاک اروپا EUROSEM | GAEA Technologies WinSieve | GEOEAS | GSLIB | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Gstat | IBM SPSS Statistics | LandSerf | Leica Geosystems ERDAS IMAGINE | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | برنامه توصیف PEDON خدمات حفاظت از منابع ملی NRCS | کاوشگر خاک خدمات حفاظت از منابع ملی NRCS | سیستم اطلاعات خاک ملی NASIS | PC-Progress HYDRUS | PedonCE | R | SAS | SGeMS | SPAW | STATISTICA | پایگاه‌های داده اطلاعات خاک | SoilVision Systems SVOFFICE | UNSATFLOW | تخمین واریوگرام و پیش‌بینی فضایی به علاوه خطا Vesper | پروژه پیش‌بینی فرسایش آب WEPP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخنوری | درک مطلب | یادگیری فعال | تفکر انتقادی | علوم | گوش دادن فعال | نوشتن | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | رایانه‌ها و الکترونیک | شیمی | ریاضیات | آموزش و پرورش | جغرافیا | ارتباطات و رسانه | مهندسی و فناوری | مدیریت و اداره | فیزیک | خدمات مشتری و شخصی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | رایانه و الکترونیک | شیمی | ریاضیات | آموزش و پرورش | جغرافیا | ارتباطات و رسانه | مهندسی و فناوری | مدیریت و اداره | فیزیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | خلاقیت | حساسیت به مسئله | دید نزدیک | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | تسهیل اعداد | استدلال ریاضی | دید دور | توجه انتخابی | سرعت ادراکی</t>
+          <t>استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | اصالت | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | بینایی دور | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | اهمیت دقیق یا صحیح بودن | محیط خارجی، قرار گرفتن در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارکنان | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقیق یا درست بودن | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان علوم دامی | تکنسین‌های بیولوژیکی | زیست‌شناسان | دانشمندان حفاظت | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران مزرعه و کارگران، محصولات زراعی، نهالستان و گلخانه | دانشمندان و تکنولوژیست‌های علوم غذایی | تکنسین‌های جنگل و حفاظت | جنگل‌بانان | زمین‌شناسان، به جز هیدرولوژیست‌ها و جغرافیدانان | هیدرولوژیست‌ها | اکولوژیست‌های صنعتی | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق | مدیران مراتع</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان علوم دامی | تکنسین‌های زیستی | زیست‌شناسان | دانشمندان حفاظت | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | دانشمندان و تکنولوژیست‌های علوم غذایی | تکنسین‌های جنگل و حفاظت | جنگل‌بانان | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | آب‌شناسان | بوم‌شناسان صنعتی | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق | مدیران مراتع</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار گرافیک سه‌بعدی | Accelrys Cerius2 | Accelrys FELIX | Accelrys Insight II | Accelrys QAUNTA | Adobe Photoshop | نرم‌افزار تحلیل و ساخت | ساخت مدل به کمک اصلاح انرژی AMBER | AutoQuant AutoDeblur | ابزار جستجوی محلی هم‌ترازی پایه BLAST | نرم‌افزار انتقال با واسطه حامل | Chang Bioscience ToolKit | ChemInnovation Software Chem 4-D | مکانیک مولکولی شیمی در هاروارد CHARMm | سیستم کریستالوگرافی و NMR (CNS) | نرم‌افزار کریستالوگرافی | Dassault Systemes Abaqus | نرم‌افزار اتصال و اتصال لیگاند | ESRI What if? | نرم‌افزار دفترچه یادداشت آزمایشگاهی الکترونیکی | Elsevier MDL ISIS/Draw | نرم‌افزار ایمیل | نرم‌افزار بیان توالی DNA و پروتئین | زبان نشانه‌گذاری توسعه‌پذیر XML | Fujitsu BioMedCache | Fujitsu MOPAC | GE Healthcare ImageQuant TL | GEPASI | نرم‌افزار Gaussian | نرم‌افزار گروه رایانه ژنتیک GSG | Golden Helix ChemTree | Golden Helix HelixTree | نرم‌افزار گرافیک | نرم‌افزار مدل Hodgkin-Huxley | IBM SPSS Statistics | Intelligent Imaging Innovations SlideBook | ItemTracker | JustBio SeqPainter | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Linux | نرم‌افزار انتشار ماکروسکوپی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Minitab | Molecular Devices Corporation MetaFluor | Molecular Devices Corporation MetaMorph | مسیرهای بیوشیمیایی Molecular Networks GmbH | Molecular Simulations WebLab ViewerPro | نرم‌افزار شبیه‌سازی مولکولی | نرم‌افزار برنامه آماری چندمتغیره MVSP | PREMIER Biosoft Array Designer | Perl | Python | R | نرم‌افزار SAP | SAS | Semichem AMPAC | نرم‌افزار پایگاه داده توالی | Shrodinger Jaguar | نرم‌افزار آماری | نرم‌افزار پیش‌بینی ساختار | The MathWorks MATLAB | Tripos SYBYL | نرم‌افزار تحلیل ویدیو | نرم‌افزار کانال‌های یونی دریچه‌دار ولتاژی | Wavefunction Spartan | Wavefunction Titan | نرم‌افزار واقعیت مصنوعی علمی دیگر YASARA</t>
+          <t>نرم‌افزار گرافیک سه‌بعدی | Accelrys Cerius2 | Accelrys FELIX | Accelrys Insight II | Accelrys QAUNTA | Adobe Photoshop | نرم‌افزار تحلیل و ساخت | ساخت مدل به کمک اصلاح انرژی AMBER | AutoQuant AutoDeblur | ابزار Basic Local Alignment Search Tool BLAST | نرم‌افزار انتقال با واسطه حامل | Chang Bioscience ToolKit | ChemInnovation Software Chem 4-D | مکانیک مولکولی شیمی در هاروارد CHARMm | سیستم کریستالوگرافی و NMR (CNS) | نرم‌افزار کریستالوگرافی | Dassault Systemes Abaqus | نرم‌افزار اتصال و اتصال لیگاند | ESRI What if? | نرم‌افزار دفترچه یادداشت آزمایشگاهی الکترونیکی | Elsevier MDL ISIS/Draw | نرم‌افزار ایمیل | نرم‌افزار بیان توالی DNA و پروتئین | زبان نشانه‌گذاری توسعه‌پذیر XML | Fujitsu BioMedCache | Fujitsu MOPAC | GE Healthcare ImageQuant TL | GEPASI | نرم‌افزار Gaussian | نرم‌افزار گروه رایانه ژنتیک GSG | Golden Helix ChemTree | Golden Helix HelixTree | نرم‌افزار گرافیکی | نرم‌افزار مدل Hodgkin-Huxley | IBM SPSS Statistics | Intelligent Imaging Innovations SlideBook | ItemTracker | JustBio SeqPainter | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Linux | نرم‌افزار انتشار ماکروسکوپی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Minitab | Molecular Devices Corporation MetaFluor | Molecular Devices Corporation MetaMorph | مسیرهای بیوشیمیایی Molecular Networks GmbH | Molecular Simulations WebLab ViewerPro | نرم‌افزار شبیه‌سازی مولکولی | نرم‌افزار برنامه آماری چندمتغیره MVSP | PREMIER Biosoft Array Designer | Perl | Python | R | نرم‌افزار SAP | SAS | Semichem AMPAC | نرم‌افزار پایگاه داده توالی | Shrodinger Jaguar | نرم‌افزار آماری | نرم‌افزار پیش‌بینی ساختار | The MathWorks MATLAB | Tripos SYBYL | نرم‌افزار تحلیل ویدیو | نرم‌افزار کانال‌های یونی دریچه‌دار ولتاژی | Wavefunction Spartan | Wavefunction Titan | نرم‌افزار واقعیت مصنوعی علمی دیگر YASARA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>علوم | درک مطلب | تفکر انتقادی | نوشتن | سخنوری | یادگیری فعال | گوش دادن فعال | استراتژی‌های یادگیری | ریاضیات | نظارت</t>
+          <t>علوم | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | گوش دادن فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | رایانه‌ها و الکترونیک | مهندسی و فناوری</t>
+          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | رایانه و الکترونیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان نوشتاری | درک نوشتاری | درک شنیداری | بیان شفاهی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید نزدیک | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | روانی ایده‌ها | خلاقیت | انعطاف‌پذیری بستار | تسهیل اعداد | تجسم | سرعت ادراکی | تشخیص گفتار | توجه انتخابی | سرعت بستار | حفظ کردن</t>
+          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | توانایی عددی | تجسم | سرعت ادراکی | تشخیص گفتار | توجه انتخابی | سرعت بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | سطح رقابت | سلامت و ایمنی سایر کارکنان | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تکرار تصمیم‌گیری | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت تکرار کارهای مشابه</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سطح رقابت | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دانشمندان علوم دامی | مهندسان زیستی و مهندسان پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیولوژیکی | زیست‌شناسان | معلمان شیمی، پس از متوسطه | شیمی‌دانان | تکنولوژیست‌های سیتوژنتیک | دانشمندان داده | ژنتیک‌دانان | تکنسین‌های بافت‌شناسی | تکنولوژیست‌های بافت‌شناسی | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | تکنسین‌های پزشکی و آزمایشگاه بالینی | تکنولوژیست‌های پزشکی و آزمایشگاه بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم‌ها | تکنولوژیست‌ها و تکنسین‌های مهندسی نانوتکنولوژی | فیزیک‌دانان</t>
+          <t>دانشمندان علوم دامی | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های زیستی | زیست‌شناسان | مدرسان شیمی، پس از متوسطه | شیمی‌دانان | تکنولوژیست‌های سیتوژنتیک | دانشمندان داده | ژنتیک‌دان‌ها | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | فیزیکدانان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0021_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0021_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | ریاضیات | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | مکانیک | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | ترابری و حمل‌ونقل | طراحی | خدمات مشتریان و خدمات فردی | آموزش و تدریس</t>
+          <t>مهندسی و فناوری | مکانیک | رایانه و الکترونیک | ریاضیات | زبان انگلیسی | فیزیک | حمل و نقل | طراحی | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | استدلال استقرایی | درک شفاهی | مرتب‌سازی اطلاعات | بیان شفاهی | چابکی انگشتان | انعطاف‌پذیری طبقه‌بندی | بیان کتبی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | ثبات دست و بازو | چابکی دستی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری بستار | دید دور | دقت کنترل | استدلال ریاضی | ابتکار و اصالت | سیالی ایده‌ها</t>
+          <t>درک کتبی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | درک شفاهی | ترتیب‌دهی اطلاعات | بیان شفاهی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | بیان کتبی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | ثبات دست و بازو | مهارت دستی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور | دقت کنترل | استدلال ریاضی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فنی مهندسی و عملیات هوافضا | مهندسان هوافضا | مهندسان خودرو | تکنسین‌ها و مکانیک‌های تعمیر و خدمات خودرو | تکنسین‌های اویونیک | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات ترابری | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به غیر از رایانه | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | مهندسان صنایع | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | مهندسان خودرو | مکانیک و تکنسین خدمات خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک و اپتیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | فیزیک | مکانیک | زبان انگلیسی | تولید و فراوری | طراحی</t>
+          <t>ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | فیزیک | مکانیک | زبان انگلیسی | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل | هماهنگی اندام‌ها | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فنی مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | تکنسین‌های شیمی | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | مونتاژکاران تجهیزات برقی و الکترونیکی | نصاب‌ها و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات ترابری | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به غیر از رایانه | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌های شیمی | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | تکنسین‌های فوتونیک و اپتیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | رایانه و الکترونیک | فیزیک | مکانیک | زبان انگلیسی | طراحی | تولید و فراوری</t>
+          <t>مهندسی و فناوری | ریاضیات | رایانه و الکترونیک | فیزیک | مکانیک | زبان انگلیسی | طراحی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل | هماهنگی اندام‌ها | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان آزمون‌های غیرمخرب NDT | تکنسین‌های فوتونیک | تکنسین‌ها و کارشناسان فنی مهندسی عمران | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | تکنسین‌ها و کارشناسان فنی مهندسی محیط زیست | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان فنی مهندسی و عملیات هوافضا | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های رباتیک | تکنسین‌ها و کارشناسان فنی مهندسی فناوری نانو | تکنسین‌های مهندسی خودرو | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | نقشه‌کشان معماری و عمران | نقشه‌کشان مکانیک | نقشه‌کشان برق و الکترونیک | مهندسان صنایع | مهندسان مکانیک | مدیران سیستم‌های کنترل کیفیت</t>
+          <t>متخصصان آزمون‌های غیرمخرب NDT | تکنسین‌های فوتونیک و اپتیک | کارشناسان و تکنسین‌های مهندسی عمران | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی محیط زیست | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های رباتیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های مهندسی خودرو | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | نقشه‌کشان معماری و عمران | نقشه‌کشان مکانیک | نقشه‌کشان برق و الکترونیک | مهندسان صنایع | مهندسان مکانیک | مدیران سیستم‌های کنترل کیفیت</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری | سخن گفتن | ریاضیات | علوم تجربی</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری | سخن گفتن | ریاضیات | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | زبان انگلیسی | فیزیک | آموزش و تدریس | رایانه و الکترونیک | تولید و فراوری | خدمات مشتریان و خدمات فردی | مکانیک | مدیریت و امور اداری | ایمنی و امنیت عمومی | طراحی | ساختمان و سازه</t>
+          <t>مهندسی و فناوری | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | رایانه و الکترونیک | تولید و فرآوری | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | ایمنی و امنیت عمومی | طراحی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک کتبی | استدلال قیاسی | درک شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان شفاهی | دید دور | بیان کتبی | وضوح گفتار | انعطاف‌پذیری بستار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | دقت کنترل | توجه انتخابی | تجسم فضایی | سرعت ادراک | ثبات دست و بازو | تشخیص رنگ | چابکی دستی | سرعت بستار | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک کتبی | استدلال قیاسی | درک شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی | بینایی دور | بیان کتبی | وضوح گفتار | انعطاف‌پذیری بستار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | دقت کنترل | توجه انتخابی | تجسم | سرعت ادراکی | ثبات دست و بازو | تشخیص رنگ بصری | مهارت دستی | سرعت بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فنی مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان فنی مهندسی محیط زیست | تکنسین‌های زمین‌شناسی، به‌جز تکنسین‌های آب‌شناسی | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | مهندسان صنایع | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | مهندسان مکانیک | تکنسین‌ها و کارشناسان فنی مهندسی فناوری نانو | تکنسین‌های پایش پرتوی و هسته‌ای | تکنسین‌های فوتونیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | کارشناسان و تکنسین‌های مهندسی محیط زیست | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های پایش و حفاظت پرتوی | تکنسین‌های فوتونیک و اپتیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | مکانیک | زبان انگلیسی | تولید و فراوری | فیزیک | خدمات مشتریان و خدمات فردی</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | مکانیک | زبان انگلیسی | تولید و فرآوری | فیزیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | حساسیت به مسئله | درک کتبی | مرتب‌سازی اطلاعات | چابکی انگشتان | بیان شفاهی | بیان کتبی | استدلال قیاسی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | دقت کنترل | چابکی دستی | ثبات دست و بازو | تجسم فضایی | تشخیص گفتار | تشخیص رنگ | توجه انتخابی | وضوح گفتار</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | مهارت انگشتان | بیان شفاهی | بیان کتبی | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | دقت کنترل | مهارت دستی | ثبات دست و بازو | تجسم | تشخیص گفتار | تشخیص رنگ بصری | توجه انتخابی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فنی مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات ترابری | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به غیر از رایانه | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | مهندسان میکروسیستم‌ها | تکنسین‌ها و کارشناسان فنی مهندسی فناوری نانو | تکنسین‌های آزمایشگاه عینک‌سازی و اپتیک | مهندسان فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | تعمیرکاران تجهیزات پزشکی | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | مهندسان فوتونیک | مهندسان رباتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | ریاضیات | نظارت | شنیدن فعال | سخن گفتن | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | ریاضیات | نظارت | گوش دادن فعال | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | جغرافیا | ریاضیات | زبان انگلیسی | مهندسی و فناوری | طراحی | خدمات مشتریان و خدمات فردی</t>
+          <t>رایانه و الکترونیک | جغرافیا | ریاضیات | زبان انگلیسی | مهندسی و فناوری | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | بیان کتبی | انعطاف‌پذیری بستار | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | دید دور | سیالی ایده‌ها</t>
+          <t>درک کتبی | بینایی نزدیک | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | بینایی دور | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | تکنسین‌ها و کارشناسان فنی کالیبراسیون | نقشه‌نگاران و متخصصان فتوگرامتری | تکنسین‌ها و کارشناسان فنی مهندسی عمران | مهندسان عمران | دانشمندان داده | نقشه‌کشان برق و الکترونیک | نقشه‌برداران ژئودزی | جغرافیدانان | تکنسین‌ها و کارشناسان فنی سامانه‌های اطلاعات جغرافیایی GIS | تکنسین‌های زمین‌شناسی، به‌جز تکنسین‌های آب‌شناسی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی | آب‌شناسان | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | دانشمندان و کارشناسان سنجش از دور | تکنسین‌های سنجش از دور | دستیاران آمار | نقشه‌برداران | تکنسین‌های ترافیک</t>
+          <t>نقشه‌کشان معماری و عمران | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان نقشه‌نگاری و فتوگرامتری | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | دانشمندان داده | نقشه‌کشان برق و الکترونیک | مهندسان نقشه‌برداری ژئودزی | جغرافیدانان | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | دستیاران و تکنسین‌های آمار | مهندسان نقشه‌برداری | تکنسین‌های ترافیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم تجربی | نگارش | تفکر انتقادی | یادگیری فعال | شنیدن فعال | سخن گفتن | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | علوم | نگارش | تفکر انتقادی | یادگیری فعال | گوش دادن فعال | سخن گفتن | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | ریاضیات | زبان انگلیسی | شیمی | تولیدات کشاورزی و دامی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | فروش و بازاریابی | مدیریت و امور اداری</t>
+          <t>زیست‌شناسی | ریاضیات | زبان انگلیسی | شیمی | تولید مواد غذایی | آموزش و پرورش | خدمات مشتری و شخصی | رایانه و الکترونیک | فروش و بازاریابی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | دید نزدیک | تشخیص گفتار | سیالی ایده‌ها | ابتکار و اصالت | استدلال ریاضی | توانایی کار با اعداد | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستار | دید دور</t>
+          <t>وضوح گفتار | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | اصالت | استدلال ریاضی | توانایی عددی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بازرسان محصولات کشاورزی و دامی | مدرسان علوم کشاورزی و دامی، آموزش عالی | تکنسین‌های کشاورزی و دامپروری | اصلاح‌کنندگان نژاد دام و حیوانات | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | تکنسین‌های زیست‌شناسی | زیست‌شناسان | تکنسین‌های تغذیه و رژیم‌درمانی | کارشناسان تغذیه و رژیم‌درمانی | مدیران مزارع، دامداری‌ها و سایر واحدهای کشاورزی | کارگران مزارع، دامداری‌ها و آبزی‌پروری | تکنسین‌های صنایع غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | متخصصان ژنتیک | میکروبیولوژیست‌ها | متخصصان خاک‌شناسی و علوم گیاهی | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فنی دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کشاورزی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | تکنسین‌های علوم زیستی | زیست‌شناسان | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | مدیران امور کشاورزی، دامپروری و شیلات | کارگران پرورش دام، طیور و آبزیان | تکنسین‌های علوم و صنایع غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | متخصصان ژنتیک | میکروبیولوژیست‌ها | متخصصان خاک‌شناسی و علوم گیاهی | دامپزشکان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | علوم تجربی | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>یادگیری فعال | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | علوم | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | تولیدات کشاورزی و دامی | شیمی | زبان انگلیسی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری | آموزش و تدریس | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | امور اداری و دفتری</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | شیمی | زبان انگلیسی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | رایانه و الکترونیک | مدیریت و اداره | آموزش و پرورش | خدمات مشتری و شخصی | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | سیالی ایده‌ها | ابتکار و اصالت | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توانایی کار با اعداد | استدلال ریاضی | سرعت ادراک | تشخیص رنگ | دید دور | سرعت بستار | توجه انتخابی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | سرعت ادراکی | تشخیص رنگ بصری | بینایی دور | سرعت بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | بازرسان محصولات کشاورزی و دامی | تکنسین‌های کشاورزی و دامپروری | متخصصان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه فناوری و محصولات سوخت زیستی | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | آشپزان رستوران | تکنسین‌های صنایع غذایی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | مهندسان ایمنی و بهداشت حرفه‌ای، به‌جز مهندسان و بازرسان ایمنی معدن | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | مهندسان صنایع | میکروبیولوژیست‌ها | کارشناسان کنترل کیفیت | متخصصان خاک‌شناسی و علوم گیاهی</t>
+          <t>مهندسان کشاورزی | بازرسان محصولات و فرآورده‌های کشاورزی | تکنسین‌های کشاورزی | متخصصان علوم دامی | تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | آشپزان رستوران | تکنسین‌های علوم و صنایع غذایی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | بوم‌شناسان صنعتی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | میکروبیولوژیست‌ها | کارشناسان تحلیل کنترل کیفیت | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | علوم تجربی | شنیدن فعال | نگارش | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | رایانه و الکترونیک | شیمی | ریاضیات | آموزش و تدریس | جغرافیا | ارتباطات و رسانه | مهندسی و فناوری | مدیریت و امور اداری | فیزیک | خدمات مشتریان و خدمات فردی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | رایانه و الکترونیک | شیمی | ریاضیات | آموزش و پرورش | جغرافیا | ارتباطات و رسانه | مهندسی و فناوری | مدیریت و اداره | فیزیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ابتکار و اصالت | حساسیت به مسئله | دید نزدیک | وضوح گفتار | سیالی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی کار با اعداد | استدلال ریاضی | دید دور | توجه انتخابی | سرعت ادراک</t>
+          <t>استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | اصالت | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | بینایی دور | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی و دامپروری | متخصصان علوم دامی | تکنسین‌های زیست‌شناسی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم زیست‌محیطی و حفاظت، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مدیران مزارع، دامداری‌ها و سایر واحدهای کشاورزی | کارگران زراعت، باغبانی، نهالستان و گلخانه | متخصصان و کارشناسان علوم و صنایع غذایی | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | جنگل‌داران | زمین‌شناسان، به‌جز آب‌شناسان و جغرافیدانان | آب‌شناسان | بوم‌شناسان صنعتی | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق | مدیران مرتع و مرتع‌داران</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | متخصصان علوم دامی | تکنسین‌های علوم زیستی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | متخصصان و کارشناسان علوم و صنایع غذایی | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق | مدیران و کارشناسان مدیریت مراتع</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>علوم تجربی | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | شنیدن فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
+          <t>علوم | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | گوش دادن فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | فیزیک | آموزش و تدریس | رایانه و الکترونیک | مهندسی و فناوری</t>
+          <t>زیست‌شناسی | شیمی | ریاضیات | زبان انگلیسی | فیزیک | آموزش و پرورش | رایانه و الکترونیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | استدلال ریاضی | دید نزدیک | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | سیالی ایده‌ها | ابتکار و اصالت | انعطاف‌پذیری بستار | توانایی کار با اعداد | تجسم فضایی | سرعت ادراک | تشخیص گفتار | توجه انتخابی | سرعت بستار | حفظ کردن اطلاعات</t>
+          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | توانایی عددی | تجسم | سرعت ادراکی | تشخیص گفتار | توجه انتخابی | سرعت بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان علوم دامی | مهندسان زیستی و مهندسان پزشکی | متخصصان بیوانفورماتیک | تکنسین‌های زیست‌شناسی | زیست‌شناسان | مدرسان شیمی، آموزش عالی | شیمی‌دانان | تکنسین‌های سیتوژنتیک | دانشمندان داده | متخصصان ژنتیک | تکنسین‌های بافت‌شناسی | متخصصان تکنولوژی بافت | دانشمندان علوم پزشکی، به‌جز اپیدمیولوژیست‌ها | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | تکنسین‌ها و کارشناسان فنی مهندسی فناوری نانو | فیزیک‌دانان</t>
+          <t>متخصصان علوم دامی | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های علوم زیستی | زیست‌شناسان | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | شیمی‌دانان | کارشناسان سیتوژنتیک | دانشمندان داده | متخصصان ژنتیک | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | فیزیک‌دانان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
